--- a/data/agreement/agreement.xlsx
+++ b/data/agreement/agreement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gretagorzoni/Desktop/antonym-detection/data/agreement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CED80A6-1A7E-E446-B626-B3FD7D7317DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4606AA-2E9D-7041-B54D-B7CF6EDB20A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="1480" windowWidth="28040" windowHeight="17440" activeTab="3" xr2:uid="{CF31EE33-3F32-FA47-9690-EA56EE1D1144}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{CF31EE33-3F32-FA47-9690-EA56EE1D1144}"/>
   </bookViews>
   <sheets>
     <sheet name="ita_pos_sampled" sheetId="2" r:id="rId1"/>
@@ -8341,7 +8341,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048576" xr:uid="{578DB5D0-C618-E949-BC2D-0434CF3FC7AE}">
-      <formula1>"ANTONYM, NOT_ANTONYM, IDIOSYNCRATIC, ERROR"</formula1>
+      <formula1>"ANTONYM, NOT_ANTONYM, IDIOSYNCRATIC, ERROR, NOMINAL"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11303,7 +11303,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048576" xr:uid="{EFA4C5BC-4CDC-1947-9BB1-41EA564939FB}">
-      <formula1>"ANTONYM, NOT_ANTONYM, IDIOSYNCRATIC, ERROR"</formula1>
+      <formula1>"ANTONYM, NOT_ANTONYM, IDIOSYNCRATIC, ERROR, NOMINAL"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14265,7 +14265,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048576" xr:uid="{725D6CED-D50B-2A4F-B8F5-AA07935E499A}">
-      <formula1>"ANTONYM, NOT_ANTONYM, IDIOSYNCRATIC, ERROR"</formula1>
+      <formula1>"ANTONYM, NOT_ANTONYM, IDIOSYNCRATIC, ERROR, NOMINAL"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17225,9 +17225,12 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048576" xr:uid="{06544E2A-BEDF-BE4C-95A8-74E70C2B85F3}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576" xr:uid="{06544E2A-BEDF-BE4C-95A8-74E70C2B85F3}">
       <formula1>"ANTONYM, NOT_ANTONYM, IDIOSYNCRATIC, ERROR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1" xr:uid="{1BD5724F-5D8F-6D43-8314-13CB310D2C7F}">
+      <formula1>"ANTONYM, NOT_ANTONYM, IDIOSYNCRATIC, ERROR, NOMINAL"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
